--- a/backend/data/financials_by_company/0QY0.F.xlsx
+++ b/backend/data/financials_by_company/0QY0.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,602 +677,663 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-36175.8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1853833</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-241172</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-241172</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-3671861</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1632505</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18437818</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-2095005</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-3727510</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-850509</v>
-      </c>
-      <c r="M2" t="n">
-        <v>850509</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-3466864.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-6286954</v>
-      </c>
-      <c r="P2" t="n">
-        <v>34967317</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>43232637</v>
-      </c>
-      <c r="R2" t="n">
-        <v>43232637</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-6286954</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-6286954</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-6286954</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1666867</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-7953821</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-2615093</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-5338728</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>760709</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4578019</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-241172</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-224957</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-211472</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="n">
-        <v>224957</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-16215</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-850509</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>-3486338</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16529499</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1632505</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1632505</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14896994</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1810617</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>13086377</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2160286</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10926091</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13043161</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>18437818</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>31480979</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>31480979</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2575.474834</v>
+        <v>-546417.9549</v>
       </c>
       <c r="C3" t="n">
-        <v>0.022749</v>
+        <v>0.2621</v>
       </c>
       <c r="D3" t="n">
-        <v>-6770998</v>
+        <v>-8425733</v>
       </c>
       <c r="E3" t="n">
-        <v>-113215</v>
+        <v>-2084769</v>
       </c>
       <c r="F3" t="n">
-        <v>-113215</v>
+        <v>-2084769</v>
       </c>
       <c r="G3" t="n">
-        <v>-8039853</v>
+        <v>-11348564</v>
       </c>
       <c r="H3" t="n">
-        <v>1998292</v>
+        <v>658660</v>
       </c>
       <c r="I3" t="n">
-        <v>16940628</v>
+        <v>17476865</v>
       </c>
       <c r="J3" t="n">
-        <v>-6884213</v>
+        <v>-10510502</v>
       </c>
       <c r="K3" t="n">
-        <v>-8882505</v>
+        <v>-11169162</v>
       </c>
       <c r="L3" t="n">
-        <v>-131484</v>
+        <v>-84689</v>
       </c>
       <c r="M3" t="n">
-        <v>131484</v>
+        <v>84689</v>
       </c>
       <c r="N3" t="n">
-        <v>-7929213.474834</v>
+        <v>-9810212.9549</v>
       </c>
       <c r="O3" t="n">
-        <v>-8977265</v>
+        <v>-11348564</v>
       </c>
       <c r="P3" t="n">
-        <v>36282378</v>
+        <v>36253977</v>
       </c>
       <c r="Q3" t="n">
-        <v>38545591</v>
+        <v>34871856</v>
       </c>
       <c r="R3" t="n">
-        <v>38545591</v>
+        <v>34871856</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="U3" t="n">
-        <v>-8977265</v>
+        <v>-11348564</v>
       </c>
       <c r="V3" t="n">
-        <v>-8977265</v>
+        <v>-11348564</v>
       </c>
       <c r="W3" t="n">
-        <v>-8977265</v>
+        <v>-11348564</v>
       </c>
       <c r="X3" t="n">
-        <v>769081</v>
+        <v>2005</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9746346</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-937412</v>
-      </c>
+        <v>-11350569</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-8808934</v>
+        <v>-11350569</v>
       </c>
       <c r="AB3" t="n">
-        <v>-205055</v>
+        <v>96718</v>
       </c>
       <c r="AC3" t="n">
-        <v>-9013989</v>
+        <v>-11253851</v>
       </c>
       <c r="AD3" t="n">
-        <v>-113215</v>
+        <v>-2084769</v>
       </c>
       <c r="AE3" t="n">
-        <v>-86283</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>-2252153</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-12437</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>86283</v>
+        <v>3269882</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-1005292</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-26932</v>
+        <v>167384</v>
       </c>
       <c r="AK3" t="n">
-        <v>-131484</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>131484</v>
-      </c>
+        <v>-84689</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-8769290</v>
+        <v>-9084393</v>
       </c>
       <c r="AN3" t="n">
-        <v>19341750</v>
+        <v>18777112</v>
       </c>
       <c r="AO3" t="n">
-        <v>1998292</v>
+        <v>658660</v>
       </c>
       <c r="AP3" t="n">
-        <v>1998292</v>
+        <v>658660</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17343458</v>
+        <v>18118452</v>
       </c>
       <c r="AR3" t="n">
-        <v>2898569</v>
+        <v>4776084</v>
       </c>
       <c r="AS3" t="n">
-        <v>14444889</v>
+        <v>13342368</v>
       </c>
       <c r="AT3" t="n">
-        <v>4640190</v>
+        <v>4406700</v>
       </c>
       <c r="AU3" t="n">
-        <v>9804699</v>
+        <v>8935668</v>
       </c>
       <c r="AV3" t="n">
-        <v>10572460</v>
+        <v>9692719</v>
       </c>
       <c r="AW3" t="n">
-        <v>16940628</v>
+        <v>17476865</v>
       </c>
       <c r="AX3" t="n">
-        <v>27513088</v>
+        <v>27169584</v>
       </c>
       <c r="AY3" t="n">
-        <v>27513088</v>
+        <v>27169584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-546417.9549</v>
+        <v>-2575.474834</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2621</v>
+        <v>0.022749</v>
       </c>
       <c r="D4" t="n">
-        <v>-8425733</v>
+        <v>-6770998</v>
       </c>
       <c r="E4" t="n">
-        <v>-2084769</v>
+        <v>-113215</v>
       </c>
       <c r="F4" t="n">
-        <v>-2084769</v>
+        <v>-113215</v>
       </c>
       <c r="G4" t="n">
-        <v>-11348564</v>
+        <v>-8039853</v>
       </c>
       <c r="H4" t="n">
-        <v>658660</v>
+        <v>1998292</v>
       </c>
       <c r="I4" t="n">
-        <v>17476865</v>
+        <v>16940628</v>
       </c>
       <c r="J4" t="n">
-        <v>-10510502</v>
+        <v>-6884213</v>
       </c>
       <c r="K4" t="n">
-        <v>-11169162</v>
+        <v>-8882505</v>
       </c>
       <c r="L4" t="n">
-        <v>-84689</v>
+        <v>-131484</v>
       </c>
       <c r="M4" t="n">
-        <v>84689</v>
+        <v>131484</v>
       </c>
       <c r="N4" t="n">
-        <v>-9810212.9549</v>
+        <v>-7929213.474834</v>
       </c>
       <c r="O4" t="n">
-        <v>-11348564</v>
+        <v>-8977265</v>
       </c>
       <c r="P4" t="n">
-        <v>36253977</v>
+        <v>36282378</v>
       </c>
       <c r="Q4" t="n">
-        <v>34871856</v>
+        <v>38545591</v>
       </c>
       <c r="R4" t="n">
-        <v>34871856</v>
+        <v>38545591</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="U4" t="n">
-        <v>-11348564</v>
+        <v>-8977265</v>
       </c>
       <c r="V4" t="n">
-        <v>-11348564</v>
+        <v>-8977265</v>
       </c>
       <c r="W4" t="n">
-        <v>-11348564</v>
+        <v>-8977265</v>
       </c>
       <c r="X4" t="n">
-        <v>2005</v>
+        <v>769081</v>
       </c>
       <c r="Y4" t="n">
-        <v>-11350569</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>-9746346</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-937412</v>
+      </c>
       <c r="AA4" t="n">
-        <v>-11350569</v>
+        <v>-8808934</v>
       </c>
       <c r="AB4" t="n">
-        <v>96718</v>
+        <v>-205055</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11253851</v>
+        <v>-9013989</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2084769</v>
+        <v>-113215</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2252153</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-12437</v>
-      </c>
+        <v>-86283</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>3269882</v>
+        <v>86283</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1005292</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>167384</v>
+        <v>-26932</v>
       </c>
       <c r="AK4" t="n">
-        <v>-84689</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>-131484</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>131484</v>
+      </c>
       <c r="AM4" t="n">
-        <v>-9084393</v>
+        <v>-8769290</v>
       </c>
       <c r="AN4" t="n">
-        <v>18777112</v>
+        <v>19341750</v>
       </c>
       <c r="AO4" t="n">
-        <v>658660</v>
+        <v>1998292</v>
       </c>
       <c r="AP4" t="n">
-        <v>658660</v>
+        <v>1998292</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18118452</v>
+        <v>17343458</v>
       </c>
       <c r="AR4" t="n">
-        <v>4776084</v>
+        <v>2898569</v>
       </c>
       <c r="AS4" t="n">
-        <v>13342368</v>
+        <v>14444889</v>
       </c>
       <c r="AT4" t="n">
-        <v>4406700</v>
+        <v>4640190</v>
       </c>
       <c r="AU4" t="n">
-        <v>8935668</v>
+        <v>9804699</v>
       </c>
       <c r="AV4" t="n">
-        <v>9692719</v>
+        <v>10572460</v>
       </c>
       <c r="AW4" t="n">
-        <v>17476865</v>
+        <v>16940628</v>
       </c>
       <c r="AX4" t="n">
-        <v>27169584</v>
+        <v>27513088</v>
       </c>
       <c r="AY4" t="n">
-        <v>27169584</v>
+        <v>27513088</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>54574.63</v>
+        <v>-36163.65</v>
       </c>
       <c r="C5" t="n">
-        <v>0.265</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>-7167723</v>
+        <v>1135647</v>
       </c>
       <c r="E5" t="n">
-        <v>205942</v>
+        <v>-241091</v>
       </c>
       <c r="F5" t="n">
-        <v>205942</v>
+        <v>-241091</v>
       </c>
       <c r="G5" t="n">
-        <v>-6965733</v>
+        <v>728074</v>
       </c>
       <c r="H5" t="n">
-        <v>191755</v>
+        <v>247412</v>
       </c>
       <c r="I5" t="n">
-        <v>4621827</v>
+        <v>14007233</v>
       </c>
       <c r="J5" t="n">
-        <v>-6961781</v>
+        <v>894556</v>
       </c>
       <c r="K5" t="n">
-        <v>-7153536</v>
+        <v>647144</v>
       </c>
       <c r="L5" t="n">
-        <v>-108676</v>
+        <v>-825228</v>
       </c>
       <c r="M5" t="n">
-        <v>108676</v>
+        <v>825228</v>
       </c>
       <c r="N5" t="n">
-        <v>-7117100.37</v>
+        <v>933001.35</v>
       </c>
       <c r="O5" t="n">
-        <v>-6965733</v>
+        <v>-6286954</v>
       </c>
       <c r="P5" t="n">
-        <v>11542017</v>
+        <v>26024916</v>
       </c>
       <c r="Q5" t="n">
-        <v>24689823</v>
+        <v>43232637</v>
       </c>
       <c r="R5" t="n">
-        <v>24689823</v>
+        <v>43232637</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="U5" t="n">
-        <v>-6965733</v>
+        <v>-6286954</v>
       </c>
       <c r="V5" t="n">
-        <v>-6965733</v>
+        <v>-6286954</v>
       </c>
       <c r="W5" t="n">
-        <v>-6965733</v>
+        <v>-6286954</v>
       </c>
       <c r="X5" t="n">
-        <v>341719</v>
+        <v>1666867</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7307452</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>-7953821</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-7015028</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-7307452</v>
+        <v>-938793</v>
       </c>
       <c r="AB5" t="n">
-        <v>45240</v>
+        <v>760709</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7262212</v>
+        <v>-178084</v>
       </c>
       <c r="AD5" t="n">
-        <v>205942</v>
+        <v>-241091</v>
       </c>
       <c r="AE5" t="n">
-        <v>211472</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-211472</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
+        <v>-224957</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
+        <v>224957</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-16134</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-825228</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>825228</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>888235</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12017683</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>247412</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>247412</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11770271</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1834681</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9935590</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1457353</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8478237</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12905918</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14007233</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>26913151</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>26913151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9651.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>248199</v>
+      </c>
+      <c r="E6" t="n">
+        <v>64345</v>
+      </c>
+      <c r="F6" t="n">
+        <v>64345</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-926066</v>
+      </c>
+      <c r="H6" t="n">
+        <v>300217</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18708014</v>
+      </c>
+      <c r="J6" t="n">
+        <v>312544</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12327</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-453031</v>
+      </c>
+      <c r="M6" t="n">
+        <v>453031</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-980759.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2236248</v>
+      </c>
+      <c r="P6" t="n">
+        <v>32218365</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>48909285</v>
+      </c>
+      <c r="R6" t="n">
+        <v>48909285</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-2236248</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2236248</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-2236248</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-83272</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-2152976</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1310182</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-842794</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>402090</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-440704</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>64345</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>-5530</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-108676</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>-7359478</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6920190</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>191755</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>191755</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6728435</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1203702</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5524733</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1889619</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3635114</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-439288</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4621827</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4182539</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4182539</v>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>64345</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-453031</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>453031</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-52018</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13510351</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>300217</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>300217</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13210134</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1411697</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11798437</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2096267</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9702170</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13458333</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18708014</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>32166347</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>32166347</v>
       </c>
     </row>
   </sheetData>
@@ -1286,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK5"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,752 +1661,837 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>43414543</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43414543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1065556</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2118741</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1296274</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1781641</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-2510378</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1296274</v>
-      </c>
-      <c r="J2" t="n">
-        <v>106401</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-230699</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-177401</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1248798</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1018099</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-230699</v>
-      </c>
-      <c r="P2" t="n">
-        <v>17283133</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>121817</v>
-      </c>
-      <c r="R2" t="n">
-        <v>121817</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-72731028</v>
-      </c>
-      <c r="T2" t="n">
-        <v>55095379</v>
-      </c>
-      <c r="U2" t="n">
-        <v>55095379</v>
-      </c>
-      <c r="V2" t="n">
-        <v>13583802</v>
-      </c>
-      <c r="W2" t="n">
-        <v>91833</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>91833</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>38535</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>53298</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13491969</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>714461</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>103370</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>103370</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2026908</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>67866</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1959042</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1959042</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10647230</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10647230</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>10647230</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12335004</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1353413</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>84882</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1065575</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1065575</v>
-      </c>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>1432008</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>202956</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-769539</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>972495</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>883364</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>89131</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10981591</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1233803</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8801004</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2084873</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6716131</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-251619</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>6967750</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>946784</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>946784</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>946784</v>
-      </c>
+        <v>3247096</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>40759024</v>
+        <v>37673955</v>
       </c>
       <c r="C3" t="n">
-        <v>40759024</v>
+        <v>37673955</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>468068</v>
+        <v>482862</v>
       </c>
       <c r="F3" t="n">
-        <v>142674</v>
+        <v>5803746</v>
       </c>
       <c r="G3" t="n">
-        <v>2958907</v>
+        <v>7912456</v>
       </c>
       <c r="H3" t="n">
-        <v>-1175803</v>
+        <v>5682160</v>
       </c>
       <c r="I3" t="n">
-        <v>142674</v>
+        <v>5803746</v>
       </c>
       <c r="J3" t="n">
-        <v>313306</v>
+        <v>418109</v>
       </c>
       <c r="K3" t="n">
-        <v>2804145</v>
+        <v>7847703</v>
       </c>
       <c r="L3" t="n">
-        <v>2856996</v>
+        <v>7904700</v>
       </c>
       <c r="M3" t="n">
-        <v>1884876</v>
+        <v>7402255</v>
       </c>
       <c r="N3" t="n">
-        <v>-919269</v>
+        <v>-445448</v>
       </c>
       <c r="O3" t="n">
-        <v>2804145</v>
+        <v>7847703</v>
       </c>
       <c r="P3" t="n">
-        <v>16971976</v>
+        <v>15918156</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34310</v>
+        <v>52341</v>
       </c>
       <c r="R3" t="n">
-        <v>-34310</v>
+        <v>52341</v>
       </c>
       <c r="S3" t="n">
-        <v>-66444074</v>
+        <v>-57466809</v>
       </c>
       <c r="T3" t="n">
-        <v>52310553</v>
+        <v>49344015</v>
       </c>
       <c r="U3" t="n">
-        <v>52310553</v>
+        <v>49344015</v>
       </c>
       <c r="V3" t="n">
-        <v>8835381</v>
+        <v>8668015</v>
       </c>
       <c r="W3" t="n">
-        <v>201882</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>970796</v>
+      </c>
+      <c r="X3" t="n">
+        <v>542618</v>
+      </c>
       <c r="Y3" t="n">
-        <v>42454</v>
+        <v>206968</v>
       </c>
       <c r="Z3" t="n">
-        <v>42454</v>
+        <v>206968</v>
       </c>
       <c r="AA3" t="n">
-        <v>159428</v>
+        <v>221210</v>
       </c>
       <c r="AB3" t="n">
-        <v>106577</v>
+        <v>164213</v>
       </c>
       <c r="AC3" t="n">
-        <v>52851</v>
+        <v>56997</v>
       </c>
       <c r="AD3" t="n">
-        <v>8633499</v>
+        <v>7697219</v>
       </c>
       <c r="AE3" t="n">
-        <v>1029912</v>
+        <v>451579</v>
       </c>
       <c r="AF3" t="n">
-        <v>134765</v>
+        <v>22442</v>
       </c>
       <c r="AG3" t="n">
-        <v>134765</v>
+        <v>22442</v>
       </c>
       <c r="AH3" t="n">
-        <v>308640</v>
+        <v>261652</v>
       </c>
       <c r="AI3" t="n">
-        <v>206729</v>
+        <v>253896</v>
       </c>
       <c r="AJ3" t="n">
-        <v>101911</v>
+        <v>7756</v>
       </c>
       <c r="AK3" t="n">
         <v>7756</v>
       </c>
       <c r="AL3" t="n">
-        <v>94155</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>7160182</v>
+        <v>6961546</v>
       </c>
       <c r="AN3" t="n">
-        <v>7160182</v>
+        <v>6961546</v>
       </c>
       <c r="AO3" t="n">
-        <v>7160182</v>
+        <v>6961546</v>
       </c>
       <c r="AP3" t="n">
-        <v>10720257</v>
+        <v>16070270</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3262561</v>
+        <v>2690891</v>
       </c>
       <c r="AR3" t="n">
-        <v>160907</v>
+        <v>140873</v>
       </c>
       <c r="AS3" t="n">
-        <v>2661471</v>
+        <v>2043957</v>
       </c>
       <c r="AT3" t="n">
-        <v>2446914</v>
+        <v>2043957</v>
       </c>
       <c r="AU3" t="n">
-        <v>214557</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>440183</v>
+        <v>506061</v>
       </c>
       <c r="AW3" t="n">
-        <v>-625236</v>
+        <v>-554785</v>
       </c>
       <c r="AX3" t="n">
-        <v>1065419</v>
+        <v>1060846</v>
       </c>
       <c r="AY3" t="n">
-        <v>787363</v>
+        <v>699618</v>
       </c>
       <c r="AZ3" t="n">
-        <v>278056</v>
+        <v>361228</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>7457696</v>
+        <v>13379379</v>
       </c>
       <c r="BC3" t="n">
-        <v>894103</v>
+        <v>1073297</v>
       </c>
       <c r="BD3" t="n">
-        <v>5826880</v>
+        <v>8795131</v>
       </c>
       <c r="BE3" t="n">
-        <v>2187548</v>
+        <v>1890999</v>
       </c>
       <c r="BF3" t="n">
-        <v>3639332</v>
+        <v>6904132</v>
       </c>
       <c r="BG3" t="n">
-        <v>-116143</v>
+        <v>-113740</v>
       </c>
       <c r="BH3" t="n">
-        <v>3755475</v>
+        <v>7017872</v>
       </c>
       <c r="BI3" t="n">
-        <v>736713</v>
+        <v>3510951</v>
       </c>
       <c r="BJ3" t="n">
-        <v>736713</v>
+        <v>3510951</v>
       </c>
       <c r="BK3" t="n">
-        <v>736713</v>
-      </c>
+        <v>3510951</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>37673955</v>
+        <v>40759024</v>
       </c>
       <c r="C4" t="n">
-        <v>37673955</v>
+        <v>40759024</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>482862</v>
+        <v>468068</v>
       </c>
       <c r="F4" t="n">
-        <v>5803746</v>
+        <v>142674</v>
       </c>
       <c r="G4" t="n">
-        <v>7912456</v>
+        <v>2958907</v>
       </c>
       <c r="H4" t="n">
-        <v>5682160</v>
+        <v>-1175803</v>
       </c>
       <c r="I4" t="n">
-        <v>5803746</v>
+        <v>142674</v>
       </c>
       <c r="J4" t="n">
-        <v>418109</v>
+        <v>313306</v>
       </c>
       <c r="K4" t="n">
-        <v>7847703</v>
+        <v>2804145</v>
       </c>
       <c r="L4" t="n">
-        <v>7904700</v>
+        <v>2856996</v>
       </c>
       <c r="M4" t="n">
-        <v>7402255</v>
+        <v>1884876</v>
       </c>
       <c r="N4" t="n">
-        <v>-445448</v>
+        <v>-919269</v>
       </c>
       <c r="O4" t="n">
-        <v>7847703</v>
+        <v>2804145</v>
       </c>
       <c r="P4" t="n">
-        <v>15918156</v>
+        <v>16971976</v>
       </c>
       <c r="Q4" t="n">
-        <v>52341</v>
+        <v>-34310</v>
       </c>
       <c r="R4" t="n">
-        <v>52341</v>
+        <v>-34310</v>
       </c>
       <c r="S4" t="n">
-        <v>-57466809</v>
+        <v>-66444074</v>
       </c>
       <c r="T4" t="n">
-        <v>49344015</v>
+        <v>52310553</v>
       </c>
       <c r="U4" t="n">
-        <v>49344015</v>
+        <v>52310553</v>
       </c>
       <c r="V4" t="n">
-        <v>8668015</v>
+        <v>8835381</v>
       </c>
       <c r="W4" t="n">
-        <v>970796</v>
-      </c>
-      <c r="X4" t="n">
-        <v>542618</v>
-      </c>
+        <v>201882</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>206968</v>
+        <v>42454</v>
       </c>
       <c r="Z4" t="n">
-        <v>206968</v>
+        <v>42454</v>
       </c>
       <c r="AA4" t="n">
-        <v>221210</v>
+        <v>159428</v>
       </c>
       <c r="AB4" t="n">
-        <v>164213</v>
+        <v>106577</v>
       </c>
       <c r="AC4" t="n">
-        <v>56997</v>
+        <v>52851</v>
       </c>
       <c r="AD4" t="n">
-        <v>7697219</v>
+        <v>8633499</v>
       </c>
       <c r="AE4" t="n">
-        <v>451579</v>
+        <v>1029912</v>
       </c>
       <c r="AF4" t="n">
-        <v>22442</v>
+        <v>134765</v>
       </c>
       <c r="AG4" t="n">
-        <v>22442</v>
+        <v>134765</v>
       </c>
       <c r="AH4" t="n">
-        <v>261652</v>
+        <v>308640</v>
       </c>
       <c r="AI4" t="n">
-        <v>253896</v>
+        <v>206729</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7756</v>
+        <v>101911</v>
       </c>
       <c r="AK4" t="n">
         <v>7756</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>94155</v>
       </c>
       <c r="AM4" t="n">
-        <v>6961546</v>
+        <v>7160182</v>
       </c>
       <c r="AN4" t="n">
-        <v>6961546</v>
+        <v>7160182</v>
       </c>
       <c r="AO4" t="n">
-        <v>6961546</v>
+        <v>7160182</v>
       </c>
       <c r="AP4" t="n">
-        <v>16070270</v>
+        <v>10720257</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2690891</v>
+        <v>3262561</v>
       </c>
       <c r="AR4" t="n">
-        <v>140873</v>
+        <v>160907</v>
       </c>
       <c r="AS4" t="n">
-        <v>2043957</v>
+        <v>2661471</v>
       </c>
       <c r="AT4" t="n">
-        <v>2043957</v>
+        <v>2446914</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>214557</v>
       </c>
       <c r="AV4" t="n">
-        <v>506061</v>
+        <v>440183</v>
       </c>
       <c r="AW4" t="n">
-        <v>-554785</v>
+        <v>-625236</v>
       </c>
       <c r="AX4" t="n">
-        <v>1060846</v>
+        <v>1065419</v>
       </c>
       <c r="AY4" t="n">
-        <v>699618</v>
+        <v>787363</v>
       </c>
       <c r="AZ4" t="n">
-        <v>361228</v>
+        <v>278056</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>13379379</v>
+        <v>7457696</v>
       </c>
       <c r="BC4" t="n">
-        <v>1073297</v>
+        <v>894103</v>
       </c>
       <c r="BD4" t="n">
-        <v>8795131</v>
+        <v>5826880</v>
       </c>
       <c r="BE4" t="n">
-        <v>1890999</v>
+        <v>2187548</v>
       </c>
       <c r="BF4" t="n">
-        <v>6904132</v>
+        <v>3639332</v>
       </c>
       <c r="BG4" t="n">
-        <v>-113740</v>
+        <v>-116143</v>
       </c>
       <c r="BH4" t="n">
-        <v>7017872</v>
+        <v>3755475</v>
       </c>
       <c r="BI4" t="n">
-        <v>3510951</v>
+        <v>736713</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3510951</v>
+        <v>736713</v>
       </c>
       <c r="BK4" t="n">
-        <v>3510951</v>
-      </c>
+        <v>736713</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>31786476</v>
+        <v>43414543</v>
       </c>
       <c r="C5" t="n">
-        <v>31786476</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>43414543</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1065556</v>
+      </c>
       <c r="E5" t="n">
-        <v>453397</v>
+        <v>2118741</v>
       </c>
       <c r="F5" t="n">
-        <v>7362043</v>
+        <v>-1296274</v>
       </c>
       <c r="G5" t="n">
-        <v>11679251</v>
+        <v>1781641</v>
       </c>
       <c r="H5" t="n">
-        <v>8336230</v>
+        <v>-2510378</v>
       </c>
       <c r="I5" t="n">
-        <v>7362043</v>
+        <v>-1296274</v>
       </c>
       <c r="J5" t="n">
-        <v>390517</v>
+        <v>106401</v>
       </c>
       <c r="K5" t="n">
-        <v>11616371</v>
+        <v>-230699</v>
       </c>
       <c r="L5" t="n">
-        <v>11668379</v>
+        <v>-177401</v>
       </c>
       <c r="M5" t="n">
-        <v>11064565</v>
+        <v>-1248798</v>
       </c>
       <c r="N5" t="n">
-        <v>-551806</v>
+        <v>-1018099</v>
       </c>
       <c r="O5" t="n">
-        <v>11616371</v>
+        <v>-230699</v>
       </c>
       <c r="P5" t="n">
-        <v>11465205</v>
+        <v>17283133</v>
       </c>
       <c r="Q5" t="n">
-        <v>-69271</v>
+        <v>121817</v>
       </c>
       <c r="R5" t="n">
-        <v>-69271</v>
+        <v>121817</v>
       </c>
       <c r="S5" t="n">
-        <v>-41230375</v>
+        <v>-72731028</v>
       </c>
       <c r="T5" t="n">
-        <v>41450812</v>
+        <v>55095379</v>
       </c>
       <c r="U5" t="n">
-        <v>41450812</v>
+        <v>55095379</v>
       </c>
       <c r="V5" t="n">
-        <v>5304255</v>
+        <v>13583802</v>
       </c>
       <c r="W5" t="n">
-        <v>1974644</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1432008</v>
-      </c>
+        <v>91833</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>233473</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>233473</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>309163</v>
+        <v>91833</v>
       </c>
       <c r="AB5" t="n">
-        <v>257155</v>
+        <v>38535</v>
       </c>
       <c r="AC5" t="n">
-        <v>52008</v>
+        <v>53298</v>
       </c>
       <c r="AD5" t="n">
-        <v>3329611</v>
+        <v>13491969</v>
       </c>
       <c r="AE5" t="n">
-        <v>765498</v>
+        <v>714461</v>
       </c>
       <c r="AF5" t="n">
-        <v>19420</v>
+        <v>103370</v>
       </c>
       <c r="AG5" t="n">
-        <v>19420</v>
+        <v>103370</v>
       </c>
       <c r="AH5" t="n">
-        <v>144234</v>
+        <v>2026908</v>
       </c>
       <c r="AI5" t="n">
-        <v>133362</v>
+        <v>67866</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10872</v>
+        <v>1959042</v>
       </c>
       <c r="AK5" t="n">
-        <v>10872</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>1959042</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
       <c r="AM5" t="n">
-        <v>2400459</v>
+        <v>10647230</v>
       </c>
       <c r="AN5" t="n">
-        <v>2400459</v>
+        <v>10647230</v>
       </c>
       <c r="AO5" t="n">
-        <v>2400459</v>
+        <v>10647230</v>
       </c>
       <c r="AP5" t="n">
-        <v>16368820</v>
+        <v>12335004</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4702979</v>
+        <v>1353413</v>
       </c>
       <c r="AR5" t="n">
-        <v>47340</v>
+        <v>84882</v>
       </c>
       <c r="AS5" t="n">
-        <v>4254328</v>
+        <v>1065575</v>
       </c>
       <c r="AT5" t="n">
-        <v>1007232</v>
+        <v>1065575</v>
       </c>
       <c r="AU5" t="n">
-        <v>3247096</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>401311</v>
+        <v>202956</v>
       </c>
       <c r="AW5" t="n">
-        <v>-449640</v>
+        <v>-769539</v>
       </c>
       <c r="AX5" t="n">
-        <v>850951</v>
+        <v>972495</v>
       </c>
       <c r="AY5" t="n">
-        <v>499651</v>
+        <v>883364</v>
       </c>
       <c r="AZ5" t="n">
-        <v>351300</v>
+        <v>89131</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>11665841</v>
+        <v>10981591</v>
       </c>
       <c r="BC5" t="n">
-        <v>150341</v>
+        <v>1233803</v>
       </c>
       <c r="BD5" t="n">
-        <v>2488585</v>
+        <v>8801004</v>
       </c>
       <c r="BE5" t="n">
-        <v>332569</v>
+        <v>2084873</v>
       </c>
       <c r="BF5" t="n">
-        <v>2156016</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+        <v>6716131</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-251619</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6967750</v>
+      </c>
       <c r="BI5" t="n">
-        <v>9026915</v>
+        <v>946784</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9026915</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
+        <v>946784</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>946784</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>51903674</v>
+      </c>
+      <c r="C6" t="n">
+        <v>51903674</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1586841</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1534125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4200082</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2057664</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1534125</v>
+      </c>
+      <c r="J6" t="n">
+        <v>868421</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3481662</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3527170</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4683832</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1202170</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3481662</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17074426</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-133470</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-133470</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-70924867</v>
+      </c>
+      <c r="T6" t="n">
+        <v>57465573</v>
+      </c>
+      <c r="U6" t="n">
+        <v>57465573</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11123744</v>
+      </c>
+      <c r="W6" t="n">
+        <v>914426</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>155098</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>155098</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>759328</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>713820</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>45508</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10209318</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>698701</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>398016</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>398016</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>827513</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>154601</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>672912</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>672912</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>8285088</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8285088</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8285088</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15807576</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3540594</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>195657</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1947537</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1947537</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1175088</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-755131</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1930219</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1126892</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>803327</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12266982</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1161093</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5898982</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>64365</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5834617</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-232658</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6067275</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5206907</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5206907</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5206907</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>222312</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2358,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,631 +2783,747 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Change In Other Current Assets</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-612196</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-5677793</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7311927</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1198432</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-423444</v>
-      </c>
-      <c r="G2" t="n">
-        <v>946784</v>
-      </c>
-      <c r="H2" t="n">
-        <v>736713</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4966</v>
-      </c>
-      <c r="J2" t="n">
-        <v>205105</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-2185656</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2932721</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2932721</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-332929</v>
-      </c>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>433084</v>
-      </c>
-      <c r="P2" t="n">
+        <v>6535448</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1198432</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>1634134</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-70068</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-5198464</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5128396</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1704202</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-479329</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2183531</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-353208</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-353208</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-137821</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>208057</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>748465</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-540408</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-59413</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-59413</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-364031</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-188752</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-188752</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>217854</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-31395</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3487048</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3487048</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-263675</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-2974124</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-3076799</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>268285</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2285234</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
-        <v>760709</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>760709</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1632505</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1632505</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>-14611</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-14611</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-5338728</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>2429</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2429</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>189326</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3784037</v>
+        <v>-6043130</v>
       </c>
       <c r="C3" t="n">
-        <v>-1743701</v>
+        <v>-263089</v>
       </c>
       <c r="D3" t="n">
-        <v>1471816</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1943424</v>
+        <v>2853571</v>
       </c>
       <c r="F3" t="n">
-        <v>-1995210</v>
+        <v>-1365361</v>
       </c>
       <c r="G3" t="n">
-        <v>736713</v>
+        <v>3510951</v>
       </c>
       <c r="H3" t="n">
-        <v>3510951</v>
+        <v>6548890</v>
       </c>
       <c r="I3" t="n">
-        <v>24724</v>
+        <v>92989</v>
       </c>
       <c r="J3" t="n">
-        <v>-2798962</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-690797</v>
-      </c>
+        <v>-3130928</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1673103</v>
+        <v>3482513</v>
       </c>
       <c r="M3" t="n">
-        <v>1673103</v>
-      </c>
-      <c r="N3" t="n">
+        <v>3482513</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>892031</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>2853571</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-263089</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>1564</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1943424</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1943424</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-271885</v>
-      </c>
-      <c r="T3" t="n">
-        <v>56316</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-1415500</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1471816</v>
-      </c>
       <c r="W3" t="n">
-        <v>-328201</v>
+        <v>-263089</v>
       </c>
       <c r="X3" t="n">
-        <v>-328201</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
+        <v>-263089</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-1992441</v>
+        <v>-1935672</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1992441</v>
+        <v>-1935672</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>2769</v>
+        <v>-570311</v>
       </c>
       <c r="AD3" t="n">
-        <v>2769</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-570311</v>
       </c>
       <c r="AF3" t="n">
-        <v>-87180</v>
+        <v>-110528</v>
       </c>
       <c r="AG3" t="n">
-        <v>-87180</v>
+        <v>-110528</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1908030</v>
+        <v>-1254833</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1788827</v>
+        <v>-4677769</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1788827</v>
+        <v>-4677769</v>
       </c>
       <c r="AK3" t="n">
-        <v>3438370</v>
+        <v>652609</v>
       </c>
       <c r="AL3" t="n">
-        <v>112323</v>
+        <v>-235479</v>
       </c>
       <c r="AM3" t="n">
-        <v>198636</v>
+        <v>2261307</v>
       </c>
       <c r="AN3" t="n">
-        <v>198636</v>
+        <v>2261307</v>
       </c>
       <c r="AO3" t="n">
-        <v>159160</v>
+        <v>1667322</v>
       </c>
       <c r="AP3" t="n">
-        <v>2968251</v>
+        <v>-3040541</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3264800</v>
+        <v>-2772673</v>
       </c>
       <c r="AR3" t="n">
-        <v>87192</v>
+        <v>-959832</v>
       </c>
       <c r="AS3" t="n">
-        <v>2075371</v>
+        <v>3286170</v>
       </c>
       <c r="AT3" t="n">
-        <v>86283</v>
+        <v>3269882</v>
       </c>
       <c r="AU3" t="n">
-        <v>-197113</v>
+        <v>96718</v>
       </c>
       <c r="AV3" t="n">
-        <v>-197113</v>
+        <v>96718</v>
       </c>
       <c r="AW3" t="n">
-        <v>1998292</v>
+        <v>658660</v>
       </c>
       <c r="AX3" t="n">
-        <v>1998292</v>
+        <v>658660</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-66288</v>
+        <v>-331407</v>
       </c>
       <c r="BC3" t="n">
-        <v>-66288</v>
+        <v>-331407</v>
       </c>
       <c r="BD3" t="n">
-        <v>-9210934</v>
-      </c>
+        <v>-11350569</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-6043130</v>
+        <v>-3784037</v>
       </c>
       <c r="C4" t="n">
-        <v>-263089</v>
+        <v>-1743701</v>
       </c>
       <c r="D4" t="n">
+        <v>1471816</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1943424</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1995210</v>
+      </c>
+      <c r="G4" t="n">
+        <v>736713</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3510951</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24724</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2798962</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-690797</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1673103</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1673103</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>2853571</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1365361</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3510951</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6548890</v>
-      </c>
-      <c r="I4" t="n">
-        <v>92989</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-3130928</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>3482513</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3482513</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>892031</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>1564</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
-        <v>2853571</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>1943424</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1943424</v>
+      </c>
       <c r="S4" t="n">
-        <v>-263089</v>
+        <v>-271885</v>
       </c>
       <c r="T4" t="n">
+        <v>56316</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1415500</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1471816</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-328201</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-328201</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-263089</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-263089</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-1935672</v>
+        <v>-1992441</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1935672</v>
+        <v>-1992441</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-570311</v>
+        <v>2769</v>
       </c>
       <c r="AD4" t="n">
+        <v>2769</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>-570311</v>
-      </c>
       <c r="AF4" t="n">
-        <v>-110528</v>
+        <v>-87180</v>
       </c>
       <c r="AG4" t="n">
-        <v>-110528</v>
+        <v>-87180</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1254833</v>
+        <v>-1908030</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4677769</v>
+        <v>-1788827</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-4677769</v>
+        <v>-1788827</v>
       </c>
       <c r="AK4" t="n">
-        <v>652609</v>
+        <v>3438370</v>
       </c>
       <c r="AL4" t="n">
-        <v>-235479</v>
+        <v>112323</v>
       </c>
       <c r="AM4" t="n">
-        <v>2261307</v>
+        <v>198636</v>
       </c>
       <c r="AN4" t="n">
-        <v>2261307</v>
+        <v>198636</v>
       </c>
       <c r="AO4" t="n">
-        <v>1667322</v>
+        <v>159160</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3040541</v>
+        <v>2968251</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2772673</v>
+        <v>3264800</v>
       </c>
       <c r="AR4" t="n">
-        <v>-959832</v>
+        <v>87192</v>
       </c>
       <c r="AS4" t="n">
-        <v>3286170</v>
+        <v>2075371</v>
       </c>
       <c r="AT4" t="n">
-        <v>3269882</v>
+        <v>86283</v>
       </c>
       <c r="AU4" t="n">
-        <v>96718</v>
+        <v>-197113</v>
       </c>
       <c r="AV4" t="n">
-        <v>96718</v>
+        <v>-197113</v>
       </c>
       <c r="AW4" t="n">
-        <v>658660</v>
+        <v>1998292</v>
       </c>
       <c r="AX4" t="n">
-        <v>658660</v>
+        <v>1998292</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>-331407</v>
+        <v>-66288</v>
       </c>
       <c r="BC4" t="n">
-        <v>-331407</v>
+        <v>-66288</v>
       </c>
       <c r="BD4" t="n">
-        <v>-11350569</v>
-      </c>
+        <v>-9210934</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6343007</v>
+        <v>2205378</v>
       </c>
       <c r="C5" t="n">
-        <v>-251992</v>
+        <v>-5677793</v>
       </c>
       <c r="D5" t="n">
+        <v>7311927</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1198432</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-423444</v>
+      </c>
+      <c r="G5" t="n">
+        <v>946784</v>
+      </c>
+      <c r="H5" t="n">
+        <v>736713</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24724</v>
+      </c>
+      <c r="J5" t="n">
+        <v>185347</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5022988</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2932721</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2932721</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-332929</v>
+      </c>
+      <c r="O5" t="n">
+        <v>433084</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>11210300</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-28470</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9026915</v>
-      </c>
-      <c r="H5" t="n">
-        <v>63504</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-304778</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9268189</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>17493756</v>
-      </c>
-      <c r="M5" t="n">
-        <v>17493756</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>6535448</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>11210300</v>
+        <v>1198432</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-251992</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+        <v>1634134</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-70068</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-5198464</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5128396</v>
+      </c>
       <c r="W5" t="n">
-        <v>-251992</v>
+        <v>1704202</v>
       </c>
       <c r="X5" t="n">
-        <v>-251992</v>
+        <v>-479329</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2183531</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1911030</v>
+        <v>-353208</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1911030</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-353208</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-137821</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-1882560</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>208057</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>748465</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-1882560</v>
+        <v>-540408</v>
       </c>
       <c r="AF5" t="n">
-        <v>-28470</v>
+        <v>-59413</v>
       </c>
       <c r="AG5" t="n">
-        <v>-28470</v>
+        <v>-59413</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-364031</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6314537</v>
+        <v>2628822</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-6314537</v>
+        <v>2628822</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1399902</v>
+        <v>217854</v>
       </c>
       <c r="AL5" t="n">
-        <v>-11802</v>
+        <v>-31395</v>
       </c>
       <c r="AM5" t="n">
-        <v>-289452</v>
+        <v>3487048</v>
       </c>
       <c r="AN5" t="n">
-        <v>-289452</v>
+        <v>3487048</v>
       </c>
       <c r="AO5" t="n">
-        <v>-116405</v>
+        <v>-263675</v>
       </c>
       <c r="AP5" t="n">
-        <v>-982243</v>
+        <v>-2974124</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1030593</v>
+        <v>-3076799</v>
       </c>
       <c r="AR5" t="n">
-        <v>70109</v>
+        <v>268285</v>
       </c>
       <c r="AS5" t="n">
-        <v>2342425</v>
+        <v>2285234</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
+        <v>760709</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>760709</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>247412</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>247412</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>-211879</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-211879</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-938793</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
         <v>0</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BG5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1050641</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2829118</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1488619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2212448</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1845816</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5206907</v>
+      </c>
+      <c r="H6" t="n">
+        <v>946784</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2185</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4262308</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-569526</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5666049</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5666049</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-628201</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="AW5" t="n">
-        <v>191755</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>191755</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2429</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2429</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>189326</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-211472</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="Q6" t="n">
+        <v>2212448</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2212448</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1340499</v>
+      </c>
+      <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="BD5" t="n">
-        <v>-7307452</v>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1340499</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-2829118</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1488619</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1629390</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1629390</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>216426</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>757105</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-540679</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-323411</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-323411</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1522405</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>795175</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>795175</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-19478</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>294646</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-2362142</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2362142</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-38065</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2308395</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>881514</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>462056</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>454593</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>402090</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>402090</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>300217</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>300217</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>38491</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>109735</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-842794</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5422301</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-222312</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-71244</v>
       </c>
     </row>
   </sheetData>
@@ -3275,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EF2"/>
+  <dimension ref="A1:EH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3421,540 +3683,550 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4033,7 +4305,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Gordon Scott Paterson', 'age': 61, 'title': 'Co-Founder &amp; Chairman', 'yearBorn': 1964, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Curt Wayne Marvis', 'age': 69, 'title': 'Co-Founder, CEO &amp; Director', 'yearBorn': 1956, 'fiscalYear': 2024, 'totalPay': 346993, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Glenn  Ginsburg', 'title': 'President', 'fiscalYear': 2024, 'totalPay': 773358, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kevin Richard Williams C.A., CPA', 'age': 56, 'title': 'Chief Financial Officer', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 111996, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Kerri  Ramgren', 'title': 'VP of Operations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Karen  Kehm', 'title': 'Vice President of Communications', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jace  Sparks', 'title': 'Chief Product Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Morgan  Barclay', 'title': 'Senior Vice President of Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Gordon Scott Paterson', 'age': 61, 'title': 'Co-Founder &amp; Chairman', 'yearBorn': 1964, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Curt Wayne Marvis', 'age': 69, 'title': 'Co-Founder, CEO &amp; Director', 'yearBorn': 1956, 'fiscalYear': 2024, 'totalPay': 343865, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Glenn  Ginsburg', 'title': 'President', 'fiscalYear': 2024, 'totalPay': 766386, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kevin Richard Williams C.A., CPA', 'age': 56, 'title': 'Chief Financial Officer', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 110987, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Kerri  Ramgren', 'title': 'VP of Operations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Karen  Kehm', 'title': 'Vice President of Communications', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jace  Sparks', 'title': 'Chief Product Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Morgan  Barclay', 'title': 'Senior Vice President of Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4051,400 +4323,406 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.196</v>
+        <v>0.165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="V2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="W2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="X2" t="n">
-        <v>0.196</v>
+        <v>0.165</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.207</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="n">
         <v>83</v>
       </c>
       <c r="AE2" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8719823</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>9931669</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4.992</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.2606849</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.18138</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.196386</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>9446475</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>10657197</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4.992</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.2904629</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.18432</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.194196</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV2" t="b">
         <v>0</v>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="AW2" t="b">
+      <c r="AW2" t="n">
+        <v>6741689</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.052789997</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>43339976</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>51903710</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.09795999499999999</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>51903710</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.008645775</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>19.431458</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-1619123</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>1:12</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>1763942400</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>205.627</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.34803927</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>5071093</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>32786</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>2242185</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>33449664</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>77.259</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-0.018760001</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>-1.17265</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>4177224</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-408700</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1448838</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.12488</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-0.1144</v>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>0QY0.F</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CR2" t="b">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
-        <v>6547069</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.18656999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>45978382</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>51903710</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.09795999499999999</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>51903710</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.008696323000000001</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>20.928385</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1735603200</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1759190400</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-6079888</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="CU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1499061600000</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>1781849279</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_316027653</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>QYou Media Inc.               R</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>1.8181764</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>QYOU Media Inc.</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.0029999912</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>0.168 - 0.168</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>27</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>7.0382776</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.0209 - 0.492</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.324</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.65853655</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>34.80393</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1781499600</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1787857200</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1787857200</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1781544600</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1781544600</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1:12</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>1763942400</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-2.327</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-0.12186378</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BU2" t="n">
-        <v>4130530</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-2814001</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1120719</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>32522140</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>133.009</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>-0.17313999</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>-5.0423903</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>2362677</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>3103497</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>-1755370</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.07265000000000001</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.08653</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.14342</v>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>0QY0.F</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CS2" t="b">
+      <c r="EA2" t="n">
+        <v>-0.013380006</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.07376781</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.028385997</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.14454186</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CV2" t="n">
-        <v>1780380184</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>finmb_316027653</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-7.1428566</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1499061600000</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.013999999</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>0.182 - 0.182</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>89</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.1611</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>7.708134</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>0.0209 - 0.492</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.6300813</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-12.1863785</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1780430400</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1780430400</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.0023200065</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.01258684</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.012196004</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.06280255</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>QYou Media Inc.               R</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>QYOU Media Inc.</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
